--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128519861</v>
       </c>
       <c r="B4" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128519859</v>
       </c>
       <c r="B5" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128519866</v>
       </c>
       <c r="B8" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128519861</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128519859</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B4" t="n">
         <v>80223</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R4" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B5" t="n">
         <v>80223</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R5" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B4" t="n">
         <v>80223</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R4" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B5" t="n">
         <v>80223</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R5" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R4" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B5" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R5" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128519866</v>
       </c>
       <c r="B8" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B4" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R4" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B5" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R5" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R4" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B5" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R5" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128519866</v>
       </c>
       <c r="B8" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B4" t="n">
         <v>80258</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R4" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B5" t="n">
         <v>80258</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R5" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128519861</v>
       </c>
       <c r="B4" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128519859</v>
       </c>
       <c r="B5" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128519866</v>
       </c>
       <c r="B8" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128519862</v>
       </c>
       <c r="B2" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128519865</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B4" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R4" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519859</v>
+        <v>128519861</v>
       </c>
       <c r="B5" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722478</v>
+        <v>722451</v>
       </c>
       <c r="R5" t="n">
-        <v>7264884</v>
+        <v>7264857</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128519864</v>
       </c>
       <c r="B7" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128519863</v>
       </c>
       <c r="B9" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128519867</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>128519866</v>
       </c>
       <c r="B8" t="n">
-        <v>57827</v>
+        <v>57968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128519859</v>
       </c>
       <c r="B4" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128519868</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>133468752</v>
       </c>
       <c r="B11" t="n">
-        <v>91868</v>
+        <v>91870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -1578,7 +1578,7 @@
         <v>133468752</v>
       </c>
       <c r="B11" t="n">
-        <v>91870</v>
+        <v>91878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128519862</v>
+        <v>133468752</v>
       </c>
       <c r="B2" t="n">
-        <v>80168</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spelbacken Stenträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722391</v>
+        <v>722459</v>
       </c>
       <c r="R2" t="n">
-        <v>7265002</v>
+        <v>7264916</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128519865</v>
+        <v>128519867</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722267</v>
+        <v>722331</v>
       </c>
       <c r="R3" t="n">
-        <v>7265006</v>
+        <v>7265026</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,32 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519859</v>
+        <v>128519868</v>
       </c>
       <c r="B4" t="n">
-        <v>80479</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722478</v>
+        <v>722422</v>
       </c>
       <c r="R4" t="n">
-        <v>7264884</v>
+        <v>7264541</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519861</v>
+        <v>128519859</v>
       </c>
       <c r="B5" t="n">
-        <v>80168</v>
+        <v>80493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722451</v>
+        <v>722478</v>
       </c>
       <c r="R5" t="n">
-        <v>7264857</v>
+        <v>7264884</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1063,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128519868</v>
+        <v>128519861</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>722422</v>
+        <v>722451</v>
       </c>
       <c r="R6" t="n">
-        <v>7264541</v>
+        <v>7264857</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1160,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128519864</v>
+        <v>128519862</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>722448</v>
+        <v>722391</v>
       </c>
       <c r="R7" t="n">
-        <v>7264951</v>
+        <v>7265002</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1257,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128519866</v>
+        <v>128519863</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,46 +1272,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spelbacken Stenträsket, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>722316</v>
+        <v>722406</v>
       </c>
       <c r="R8" t="n">
-        <v>7265018</v>
+        <v>7265010</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1337,24 +1329,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 3 stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128519863</v>
+        <v>128519864</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>722406</v>
+        <v>722448</v>
       </c>
       <c r="R9" t="n">
-        <v>7265010</v>
+        <v>7264951</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1478,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128519867</v>
+        <v>128519866</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>58057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,34 +1466,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spelbacken Stenträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>722331</v>
+        <v>722316</v>
       </c>
       <c r="R10" t="n">
-        <v>7265026</v>
+        <v>7265018</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1546,9 +1535,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 3 stycken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1575,48 +1579,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133468752</v>
+        <v>128519865</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spelbacken Stenträsket, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>722459</v>
+        <v>722267</v>
       </c>
       <c r="R11" t="n">
-        <v>7264916</v>
+        <v>7265006</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1657,7 +1658,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133468752</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519867</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519868</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519859</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519861</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519864</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1576,6 +1621,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519866</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,8 +1723,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>